--- a/strojovy_kod.xlsx
+++ b/strojovy_kod.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annajungmannova/workspace/cpu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9361EFBA-77B7-9E41-AC5A-B9A82EAAB10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE56053F-D989-EA4C-BA48-456E896FCAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="880" windowWidth="25360" windowHeight="16540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
